--- a/data/incremental/incremental_04_providencia_manual.xlsx
+++ b/data/incremental/incremental_04_providencia_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/TACU+TACU+Restaurante+-+Providencia/@-33.4203473,-70.6104797,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf4b70822fe9:0xf81994fdb40ea03c!8m2!3d-33.4203473!4d-70.6104797!16s%2Fg%2F11tfz6cvsk?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/TACU+TACU+Restaurante+-+Providencia/data=!4m7!3m6!1s0x9662cf4b70822fe9:0xf81994fdb40ea03c!8m2!3d-33.4203473!4d-70.6104797!16s%2Fg%2F11tfz6cvsk!19sChIJ6S-CcEvPYpYRPKAOtP2UGfg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kil%C3%BA+-+Casa+de+Carnes/@-33.431898,-70.623884,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c5d9547e1577:0xfc5330f70249a13c!8m2!3d-33.431898!4d-70.623884!16s%2Fg%2F11wj0k0h23?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Kil%C3%BA+-+Casa+de+Carnes/data=!4m7!3m6!1s0x9662c5d9547e1577:0xfc5330f70249a13c!8m2!3d-33.431898!4d-70.623884!16s%2Fg%2F11wj0k0h23!19sChIJdxV-VNnFYpYRPKFJAvcwU_w?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,52 +1045,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Restaurant Viva La Vida</t>
+          <t>La Yunta Providencia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Constitución 166, 7520367 Providencia, Región Metropolitana</t>
+          <t>Manuel Montt 748, 7500977 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9 8438 2683</t>
+          <t>(2) 3270 0556</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.restaurantvivalavida.cl/</t>
+          <t>http://www.layunta.cl/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Viva+La+Vida/data=!4m7!3m6!1s0x9662c5900af9e0f1:0x7a3457df8c8e8df0!8m2!3d-33.4323847!4d-70.6350521!16s%2Fg%2F11bbrm9xzn!19sChIJ8eD5CpDFYpYR8I2OjN9XNHo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Yunta+Providencia/data=!4m7!3m6!1s0x9662cf7c1d4926e9:0x86997b36f37f3a27!8m2!3d-33.4349707!4d-70.6163277!16s%2Fg%2F11cpppmpkp!19sChIJ6SZJHXzPYpYRJzp_8zZ7mYY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.4323847</t>
+          <t>-33.4349707</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-70.6350521</t>
+          <t>-70.6163277</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,52 +1148,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Le Bistrot de Gaetan</t>
+          <t>Restaurant Viva La Vida</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sta. Magdalena 80, Local 7, 7510054 Providencia, Región Metropolitana</t>
+          <t>Constitución 166, 7520367 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(2) 2232 1054</t>
+          <t>9 8438 2683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://www.lebistrot.cl/</t>
+          <t>https://www.restaurantvivalavida.cl/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restaurante francés</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Le+Bistrot+de+Gaetan/@-33.4208641,-70.6100723,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf6627dc8ad1:0xe6d73bc9a7a6887!8m2!3d-33.4208641!4d-70.6100723!16s%2Fg%2F1wl4rt9r?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Viva+La+Vida/data=!4m7!3m6!1s0x9662c5900af9e0f1:0x7a3457df8c8e8df0!8m2!3d-33.4323847!4d-70.6350521!16s%2Fg%2F11bbrm9xzn!19sChIJ8eD5CpDFYpYR8I2OjN9XNHo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.4208641</t>
+          <t>-33.4323847</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.6100723</t>
+          <t>-70.6350521</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1251,52 +1251,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Yunta Providencia</t>
+          <t>La Hacienda Gaucha</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manuel Montt 748, 7500977 Providencia, Región Metropolitana</t>
+          <t>Providencia Región Metropolitana CL, Av. Pedro de Valdivia 1719, 7511282 Santiago, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2) 3270 0556</t>
+          <t>9 5396 4302</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.layunta.cl/</t>
+          <t>https://www.instagram.com/lahaciendagaucha</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante especializado en filetes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Yunta+Providencia/@-33.4349707,-70.6163277,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf7c1d4926e9:0x86997b36f37f3a27!8m2!3d-33.4349707!4d-70.6163277!16s%2Fg%2F11cpppmpkp?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Hacienda+Gaucha/data=!4m7!3m6!1s0x9662cf77d05d9733:0x50a5c2a41484f2f5!8m2!3d-33.4387109!4d-70.6083537!16s%2Fg%2F11b7q82hfy!19sChIJM5dd0HfPYpYR9fKEFKTCpVA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.4349707</t>
+          <t>-33.4387109</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-70.6163277</t>
+          <t>-70.6083537</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1354,52 +1354,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Hacienda Gaucha</t>
+          <t>Le Bistrot de Gaetan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Providencia Región Metropolitana CL, Av. Pedro de Valdivia 1719, 7511282 Santiago, Providencia, Región Metropolitana</t>
+          <t>Sta. Magdalena 80, Local 7, 7510054 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9 5396 4302</t>
+          <t>(2) 2232 1054</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lahaciendagaucha</t>
+          <t>http://www.lebistrot.cl/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Restaurante especializado en filetes</t>
+          <t>Restaurante francés</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Hacienda+Gaucha/data=!4m7!3m6!1s0x9662cf77d05d9733:0x50a5c2a41484f2f5!8m2!3d-33.4387109!4d-70.6083537!16s%2Fg%2F11b7q82hfy!19sChIJM5dd0HfPYpYR9fKEFKTCpVA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Le+Bistrot+de+Gaetan/data=!4m7!3m6!1s0x9662cf6627dc8ad1:0xe6d73bc9a7a6887!8m2!3d-33.4208641!4d-70.6100723!16s%2Fg%2F1wl4rt9r!19sChIJ0YrcJ2bPYpYRh2h6mrxzbQ4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.4387109</t>
+          <t>-33.4208641</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-70.6083537</t>
+          <t>-70.6100723</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1560,52 +1560,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Casaluz Restaurant</t>
+          <t>Ay Mi Madre Restobar Providencia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>479</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Av. Italia 805, 7501184 Providencia, Región Metropolitana</t>
+          <t>Gral Flores 218, 7750000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9 8328 3329</t>
+          <t>9 4497 8597</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.casaluzrestaurant.cl/</t>
+          <t>https://linktr.ee/Aymimadrecl</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Pub restaurante</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casaluz+Restaurant/@-33.4421855,-70.6264657,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c581e19870c3:0x9be183df6be6387c!8m2!3d-33.4421855!4d-70.6264657!16s%2Fg%2F1tx16kc6?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Ay+Mi+Madre+Restobar+Providencia/data=!4m7!3m6!1s0x9662cf31549a0e2f:0xe91ba3c5bee359c3!8m2!3d-33.426514!4d-70.6200915!16s%2Fg%2F11n08wt6lj!19sChIJLw6aVDHPYpYRw1njvsWjG-k?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.4421855</t>
+          <t>-33.426514</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-70.6264657</t>
+          <t>-70.6200915</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Giratorio/@-33.421721,-70.6085958,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf68c0b11a77:0x2943c2e12a71bae4!8m2!3d-33.421721!4d-70.6085958!16s%2Fg%2F1hjhbv_h4?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Giratorio/data=!4m7!3m6!1s0x9662cf68c0b11a77:0x2943c2e12a71bae4!8m2!3d-33.421721!4d-70.6085958!16s%2Fg%2F1hjhbv_h4!19sChIJdxqxwGjPYpYR5LpxKuHCQyk?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1766,52 +1766,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Carrer Nou</t>
+          <t>Casaluz Restaurant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Miguel Claro 1802, 7501394 Providencia, Región Metropolitana</t>
+          <t>Av. Italia 805, 7501184 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(2) 2727 1161</t>
+          <t>9 8328 3329</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/CarrerNouCL/</t>
+          <t>https://www.casaluzrestaurant.cl/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Restaurante de cocina española</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Carrer+Nou/@-33.4455205,-70.6168304,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf814b9705a5:0x7d584a20336bdc9!8m2!3d-33.4455205!4d-70.6168304!16s%2Fg%2F11ckqrj8n1?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Casaluz+Restaurant/data=!4m7!3m6!1s0x9662c581e19870c3:0x9be183df6be6387c!8m2!3d-33.4421855!4d-70.6264657!16s%2Fg%2F1tx16kc6!19sChIJw3CY4YHFYpYRfDjma9-D4Zs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.4455205</t>
+          <t>-33.4421855</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-70.6168304</t>
+          <t>-70.6264657</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1869,52 +1869,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ay Mi Madre Restobar Providencia</t>
+          <t>Carrer Nou</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gral Flores 218, 7750000 Providencia, Región Metropolitana</t>
+          <t>Miguel Claro 1802, 7501394 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9 4497 8597</t>
+          <t>(2) 2727 1161</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://linktr.ee/Aymimadrecl</t>
+          <t>https://www.facebook.com/CarrerNouCL/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pub restaurante</t>
+          <t>Restaurante de cocina española</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ay+Mi+Madre+Restobar+Providencia/data=!4m7!3m6!1s0x9662cf31549a0e2f:0xe91ba3c5bee359c3!8m2!3d-33.426514!4d-70.6200915!16s%2Fg%2F11n08wt6lj!19sChIJLw6aVDHPYpYRw1njvsWjG-k?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Carrer+Nou/data=!4m7!3m6!1s0x9662cf814b9705a5:0x7d584a20336bdc9!8m2!3d-33.4455205!4d-70.6168304!16s%2Fg%2F11ckqrj8n1!19sChIJpQWXS4HPYpYRyb02A6KE1Qc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.426514</t>
+          <t>-33.4455205</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-70.6200915</t>
+          <t>-70.6168304</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Le+Flaubert/@-33.4221115,-70.6128618,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf66f40e9c4b:0x1436ab6a7739daf5!8m2!3d-33.4221115!4d-70.6128618!16s%2Fg%2F1tz72lg5?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Le+Flaubert/data=!4m7!3m6!1s0x9662cf66f40e9c4b:0x1436ab6a7739daf5!8m2!3d-33.4221115!4d-70.6128618!16s%2Fg%2F1tz72lg5!19sChIJS5wO9GbPYpYR9do5d2qrNhQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2178,52 +2178,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Brava Restaurant</t>
+          <t>Del Beto Restaurant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Av. Providencia 1713, 7500528 Providencia, Región Metropolitana</t>
+          <t>Manuel Montt 1828, 7501280 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9 3644 3842</t>
+          <t>(2) 2209 0206</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://rest.nuvy.cl/la-brava</t>
+          <t>http://delbeto.cl/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Brava+Restaurant/@-33.4268293,-70.6150193,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf0007137975:0xfef2a0c7b5929a5c!8m2!3d-33.4268293!4d-70.6150193!16s%2Fg%2F11xn6z0qkj?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Del+Beto+Restaurant/data=!4m7!3m6!1s0x9662cf83ed3d8115:0xa4d5d3532a0430e8!8m2!3d-33.4444713!4d-70.6141735!16s%2Fg%2F1tj6w0d9!19sChIJFYE97YPPYpYR6DAEKlPT1aQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.4268293</t>
+          <t>-33.4444713</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-70.6150193</t>
+          <t>-70.6141735</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2281,52 +2281,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Del Beto Restaurant</t>
+          <t>La Brava Restaurant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manuel Montt 1828, 7501280 Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 1713, 7500528 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(2) 2209 0206</t>
+          <t>9 3644 3842</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>http://delbeto.cl/</t>
+          <t>https://rest.nuvy.cl/la-brava</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Del+Beto+Restaurant/@-33.4444713,-70.6141735,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf83ed3d8115:0xa4d5d3532a0430e8!8m2!3d-33.4444713!4d-70.6141735!16s%2Fg%2F1tj6w0d9?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Brava+Restaurant/data=!4m7!3m6!1s0x9662cf0007137975:0xfef2a0c7b5929a5c!8m2!3d-33.4268293!4d-70.6150193!16s%2Fg%2F11xn6z0qkj!19sChIJdXkTBwDPYpYRXJqStceg8v4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.4444713</t>
+          <t>-33.4268293</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-70.6141735</t>
+          <t>-70.6150193</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2384,28 +2384,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bar Liguria Manuel Montt</t>
+          <t>Eladio Restaurant Providencia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Av. Providencia 1353, 7500575 Santiago, Providencia, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Av. Nueva Providencia 2250, 7510086 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9 9530 4537</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>http://www.liguria.cl/</t>
+          <t>http://www.eladio.cl/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2415,17 +2419,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bar+Liguria+Manuel+Montt/@-33.4284996,-70.6191305,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf62e6a64093:0x7a36ab4eafc5b3a7!8m2!3d-33.4284996!4d-70.6191305!16s%2Fg%2F1hhm352mj?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Eladio+Restaurant+Providencia/data=!4m7!3m6!1s0x9662cf68bef264ff:0xeb1ffbda7ce6dec6!8m2!3d-33.421716!4d-70.6085802!16s%2Fg%2F1v2kymky!19sChIJ_2TyvmjPYpYRxt7mfNr7H-s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.4284996</t>
+          <t>-33.421716</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-70.6191305</t>
+          <t>-70.6085802</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2450,12 +2454,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2478,41 +2482,33 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Eladio Restaurant Providencia</t>
+          <t>Bar Liguria Manuel Montt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Av. Nueva Providencia 2250, 7510086 Providencia, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>9 9530 4537</t>
-        </is>
-      </c>
+          <t>Av. Providencia 1353, 7500575 Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>http://www.eladio.cl/</t>
+          <t>http://www.liguria.cl/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2522,17 +2518,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Eladio+Restaurant+Providencia/data=!4m7!3m6!1s0x9662cf68bef264ff:0xeb1ffbda7ce6dec6!8m2!3d-33.421716!4d-70.6085802!16s%2Fg%2F1v2kymky!19sChIJ_2TyvmjPYpYRxt7mfNr7H-s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Bar+Liguria+Manuel+Montt/data=!4m7!3m6!1s0x9662cf62e6a64093:0x7a36ab4eafc5b3a7!8m2!3d-33.4284996!4d-70.6191305!16s%2Fg%2F1hhm352mj!19sChIJk0Cm5mLPYpYRp7PFr06rNno?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.421716</t>
+          <t>-33.4284996</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-70.6085802</t>
+          <t>-70.6191305</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2557,12 +2553,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2585,7 +2581,11 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2693,7 +2693,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honua Poke Bar</t>
+          <t>La Antojería</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2703,42 +2703,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Av. Las Condes 7134, 7560678 Las Condes, Región Metropolitana</t>
+          <t>Eliodoro Yáñez 1049, 7500725 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(2) 2884 1768</t>
+          <t>(2) 2235 3900</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://honuapoke.cl/</t>
+          <t>https://www.laantojeria.cl/Carta-Local</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante hawaiano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Honua+Poke+Bar/data=!4m7!3m6!1s0x9662cf30d24d21fd:0x9717b0273fc65fdd!8m2!3d-33.404444!4d-70.557352!16s%2Fg%2F11gfp18h9k!19sChIJ_SFN0jDPYpYR3V_GPyewF5c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Antojer%C3%ADa/data=!4m7!3m6!1s0x9662cf7d91523a0d:0xf0c24fe0beffea5e!8m2!3d-33.4339209!4d-70.620584!16s%2Fg%2F11bwm2dztf!19sChIJDTpSkX3PYpYRXur_vuBPwvA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.404444</t>
+          <t>-33.4339209</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.557352</t>
+          <t>-70.620584</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2796,52 +2796,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alemán Experto Providencia</t>
+          <t>Siria Restaurant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Av. Pedro de Valdivia 1683, 7510592 Providencia, Región Metropolitana</t>
+          <t>Marín 415, 7501101 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2) 2906 2538</t>
+          <t>9 3089 6259</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.alemanexperto.cl/</t>
+          <t>https://www.instagram.com/siriarestaurant</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restaurante alemán</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Alem%C3%A1n+Experto+Providencia/data=!4m7!3m6!1s0x9662cf77dacbcaed:0xab19042c0872b629!8m2!3d-33.438253!4d-70.607706!16s%2Fg%2F11clsv2mfr!19sChIJ7crL2nfPYpYRKbZyCCwEGas?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Siria+Restaurant/data=!4m7!3m6!1s0x9662c566ef658ea5:0x1606d6fa9879ea99!8m2!3d-33.4442392!4d-70.626257!16s%2Fg%2F11r9g2v93m!19sChIJpY5l72bFYpYRmep5mPrWBhY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.438253</t>
+          <t>-33.4442392</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.607706</t>
+          <t>-70.626257</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2899,42 +2899,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sabko namaste</t>
+          <t>El Fogón de Momo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Manuel Montt 1584, 7501149 Providencia, Región Metropolitana</t>
+          <t>Condell 806, 7501186 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9 5887 9021</t>
+          <t>(2) 2634 7964</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.sabkonamaste.cl/</t>
+          <t>http://www.fogondemomo.cl/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Restaurante indio</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/sabko+namaste/@-33.4423407,-70.6147669,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf849b8941f3:0x338c0521d76c0517!8m2!3d-33.4423407!4d-70.6147669!16s%2Fg%2F11rxmh52ny?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/El+Fog%C3%B3n+de+Momo/data=!4m7!3m6!1s0x9662c57f56de349d:0x5e8c8b0f271ebdc6!8m2!3d-33.4423407!4d-70.6270619!16s%2Fg%2F11csr208y7!19sChIJnTTeVn_FYpYRxr0eJw-LjF4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.6147669</t>
+          <t>-70.6270619</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3002,52 +3002,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lusitano</t>
+          <t>Taipá Cevichería</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>284</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Antonio Bellet 345, 7500025 Providencia, Región Metropolitana</t>
+          <t>Dardignac 081 providencia, 8320000 Santiago, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9 7648 8018</t>
+          <t>9 4574 2092</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>http://www.lusitano.cl/</t>
+          <t>https://mi.cuaaq.com/negocio/taip%C3%A1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lusitano/@-33.4245811,-70.6190324,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfcd7e310725:0xf3f2dc9b2c4c325!8m2!3d-33.4245811!4d-70.6190324!16s%2Fg%2F11n2n3y5wr?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Taip%C3%A1+Cevicher%C3%ADa/data=!4m7!3m6!1s0x9662c5fd16871d07:0x733f82fbe132d779!8m2!3d-33.4333025!4d-70.6349334!16s%2Fg%2F11v12w5m3z!19sChIJBx2HFv3FYpYRedcy4fuCP3M?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.4245811</t>
+          <t>-33.4333025</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-70.6190324</t>
+          <t>-70.6349334</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3105,52 +3105,48 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rishtedar Providencia</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Holanda 160, 7510021 Providencia, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(2) 2231 3257</t>
-        </is>
-      </c>
+          <t>Condell 818, 7501186 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>http://www.rishtedar.cl/</t>
+          <t>http://www.elhoyo.cl/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante indio</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rishtedar+Providencia/data=!4m7!3m6!1s0x9662cf6c0972185b:0x8e07f728978b72df!8m2!3d-33.4207131!4d-70.60342!16s%2Fg%2F1tk_qgtb!19sChIJWxhyCWzPYpYR33KLlyj3B44?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+Hoyo/data=!4m7!3m6!1s0x9662c4f97cbad81d:0x4b3337cd419a8666!8m2!3d-33.4424096!4d-70.6269601!16s%2Fg%2F11dynqr31s!19sChIJHdi6fPnEYpYRZoaaQc03M0s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.4207131</t>
+          <t>-33.4424096</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.60342</t>
+          <t>-70.6269601</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3175,12 +3171,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3203,57 +3199,61 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Papelón Sabroso</t>
+          <t>Rishtedar Providencia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dentro de la plaza, del lado de - Av. Providencia 1669, 7500540 Providencia, Región Metropolitana</t>
+          <t>Holanda 160, 7510021 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9 9169 1222</t>
+          <t>(2) 2231 3257</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.papelonsabroso.com/pedir</t>
+          <t>http://www.rishtedar.cl/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante indio</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Papel%C3%B3n+Sabroso/@-33.4271201,-70.6155139,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf6483b2a03b:0xe2687b20d03f3b7f!8m2!3d-33.4271201!4d-70.6155139!16s%2Fg%2F11c1m_dxch?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rishtedar+Providencia/data=!4m7!3m6!1s0x9662cf6c0972185b:0x8e07f728978b72df!8m2!3d-33.4207131!4d-70.60342!16s%2Fg%2F1tk_qgtb!19sChIJWxhyCWzPYpYR33KLlyj3B44?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.4271201</t>
+          <t>-33.4207131</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-70.6155139</t>
+          <t>-70.60342</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3308,8 +3308,416 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Arabito Deluxe - Shawarmas - Comida Arabe - Providencia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>José Manuel Infante 1373, 7510987 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9 6254 3099</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arabitodeluxe/</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Arabito+Deluxe+-+Shawarmas+-+Comida+Arabe+-+Providencia/data=!4m7!3m6!1s0x9662cfba2bf0c559:0x7ace577283dabda1!8m2!3d-33.4435991!4d-70.6202155!16s%2Fg%2F11swynt5k6!19sChIJWcXwK7rPYpYRob3ag3JXzno?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-33.4435991</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-70.6202155</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Normandie Restaurant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Av. Providencia 1234, 7500571 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(2) 2236 3011</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.normandie1234.cl/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante francés</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Normandie+Restaurant/data=!4m7!3m6!1s0x9662cf62a3242b63:0x53f6f146ee47c6e4!8m2!3d-33.4290153!4d-70.6209767!16s%2Fg%2F1vljhjsb!19sChIJYysko2LPYpYR5MZH7kbx9lM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.4290153</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.6209767</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Restaurant Mendo's (Providencia)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Seminario 96, Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(2) 2341 8964</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurant+Mendo%27s+%28Providencia%29/data=!4m7!3m6!1s0x9662c5825ac29363:0x1ea085937e5e9fd3!8m2!3d-33.44065!4d-70.6298941!16s%2Fg%2F1q62d7s21!19sChIJY5PCWoLFYpYR059efpOFoB4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.44065</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.6298941</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sanguchería Ciudad Vieja</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Constitución 92, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(45) 298 7915</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>http://www.ciudadvieja.cl/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Sangucher%C3%ADa+Ciudad+Vieja/data=!4m7!3m6!1s0x9662c59abc9f0a3d:0x32b9af4162c156fe!8m2!3d-33.4332871!4d-70.6348386!16s%2Fg%2F11bx1h7ykt!19sChIJPQqfvJrFYpYR_lbBYkGvuTI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.4332871</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.6348386</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG27"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>